--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -36,7 +36,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>FrAssignedntity</t>
+    <t>FrAssignedEntity</t>
   </si>
   <si>
     <t>Title</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-02T14:56:23+00:00</t>
+    <t>2025-01-06T16:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -567,14 +567,14 @@
     <t>AssignedEntity.assignedPerson</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Person
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Person {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-person}
 </t>
   </si>
   <si>
     <t>AssignedEntity.representedOrganization</t>
   </si>
   <si>
-    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization
+    <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
   </si>
   <si>
@@ -2881,7 +2881,7 @@
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
@@ -3085,7 +3085,7 @@
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3186,7 +3186,7 @@
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:20:22+00:00</t>
+    <t>2025-01-06T16:22:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-06T16:22:16+00:00</t>
+    <t>2025-01-14T14:51:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T14:51:40+00:00</t>
+    <t>2025-01-14T21:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T21:51:01+00:00</t>
+    <t>2025-01-15T14:08:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-15T14:08:36+00:00</t>
+    <t>2025-01-17T15:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -313,6 +313,10 @@
     <t>InfrastructureRoot.typeId</t>
   </si>
   <si>
+    <t xml:space="preserve">II-1:An II instance must have either a root or an nullFlavor. {root.exists() or nullFlavor.exists()}
+</t>
+  </si>
+  <si>
     <t>AssignedEntity.typeId.nullFlavor</t>
   </si>
   <si>
@@ -398,6 +402,34 @@
   </si>
   <si>
     <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>AssignedEntity.id.nullFlavor</t>
+  </si>
+  <si>
+    <t>AssignedEntity.id.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>AssignedEntity.id.displayable</t>
+  </si>
+  <si>
+    <t>AssignedEntity.id.root</t>
+  </si>
+  <si>
+    <t>- Pour un professionnel : '1.2.250.1.71.4.2.1'
+- Pour le patient/usager : OID de l'autorité d'affectation de l'INS
+- Pour un système de structure : '1.2.250.1.71.4.2.1' 
+- Pour un SNR : OID de l'éditeur 
+- Pour le DP : '1.2.250.1.71.4.2.1'</t>
+  </si>
+  <si>
+    <t>A unique identifier that guarantees the global uniqueness of the instance identifier. The root alone may be the entire instance identifier.</t>
+  </si>
+  <si>
+    <t>AssignedEntity.id.extension</t>
+  </si>
+  <si>
+    <t>Valeur de l’identifiant</t>
   </si>
   <si>
     <t>AssignedEntity.sdtcIdentifiedBy</t>
@@ -887,7 +919,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK32"/>
+  <dimension ref="A1:AK37"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="44.25" customWidth="true" bestFit="true"/>
@@ -1441,7 +1473,7 @@
         <v>74</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>74</v>
@@ -1449,10 +1481,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1550,17 +1582,17 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E7" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" t="s" s="2">
         <v>80</v>
@@ -1578,11 +1610,11 @@
         <v>74</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L7" s="2"/>
       <c r="M7" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1633,7 +1665,7 @@
         <v>74</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>80</v>
@@ -1653,17 +1685,17 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E8" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="F8" t="s" s="2">
         <v>80</v>
@@ -1681,11 +1713,11 @@
         <v>74</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L8" s="2"/>
       <c r="M8" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1736,7 +1768,7 @@
         <v>74</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>80</v>
@@ -1756,17 +1788,17 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E9" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F9" t="s" s="2">
         <v>75</v>
@@ -1784,11 +1816,11 @@
         <v>74</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="L9" s="2"/>
       <c r="M9" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1797,7 +1829,7 @@
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="S9" t="s" s="2">
         <v>74</v>
@@ -1839,7 +1871,7 @@
         <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1859,17 +1891,17 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E10" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F10" t="s" s="2">
         <v>75</v>
@@ -1887,11 +1919,11 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="L10" s="2"/>
       <c r="M10" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1942,7 +1974,7 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>80</v>
@@ -1962,10 +1994,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1992,7 +2024,7 @@
       </c>
       <c r="L11" s="2"/>
       <c r="M11" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2043,7 +2075,7 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>80</v>
@@ -2063,10 +2095,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2100,7 +2132,7 @@
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S12" t="s" s="2">
         <v>74</v>
@@ -2122,7 +2154,7 @@
       </c>
       <c r="Y12" s="2"/>
       <c r="Z12" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>74</v>
@@ -2140,7 +2172,7 @@
         <v>74</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>80</v>
@@ -2160,10 +2192,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2239,7 +2271,7 @@
         <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>75</v>
@@ -2259,16 +2291,18 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" t="s" s="2">
+        <v>84</v>
+      </c>
       <c r="F14" t="s" s="2">
         <v>80</v>
       </c>
@@ -2285,10 +2319,12 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>127</v>
+        <v>85</v>
       </c>
       <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
+      <c r="M14" t="s" s="2">
+        <v>86</v>
+      </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -2314,13 +2350,11 @@
         <v>74</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y14" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y14" s="2"/>
       <c r="Z14" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -2338,13 +2372,13 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>126</v>
+        <v>89</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>74</v>
@@ -2367,12 +2401,14 @@
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" t="s" s="2">
+        <v>101</v>
+      </c>
       <c r="F15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>74</v>
@@ -2384,10 +2420,12 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>129</v>
+        <v>102</v>
       </c>
       <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
+      <c r="M15" t="s" s="2">
+        <v>103</v>
+      </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2413,11 +2451,13 @@
         <v>74</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="Y15" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y15" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z15" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>74</v>
@@ -2435,7 +2475,7 @@
         <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>128</v>
+        <v>104</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>80</v>
@@ -2455,17 +2495,17 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E16" t="s" s="2">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="F16" t="s" s="2">
         <v>80</v>
@@ -2483,11 +2523,11 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="L16" s="2"/>
       <c r="M16" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2514,11 +2554,13 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="Y16" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="Y16" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="Z16" t="s" s="2">
-        <v>88</v>
+        <v>74</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2536,7 +2578,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2556,20 +2598,20 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E17" t="s" s="2">
-        <v>62</v>
+        <v>111</v>
       </c>
       <c r="F17" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>75</v>
@@ -2584,11 +2626,13 @@
         <v>74</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="L17" s="2"/>
+        <v>112</v>
+      </c>
+      <c r="L17" t="s" s="2">
+        <v>131</v>
+      </c>
       <c r="M17" t="s" s="2">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2639,7 +2683,7 @@
         <v>74</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>115</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>80</v>
@@ -2659,20 +2703,20 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E18" t="s" s="2">
-        <v>137</v>
+        <v>117</v>
       </c>
       <c r="F18" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>75</v>
@@ -2687,11 +2731,13 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L18" s="2"/>
+        <v>102</v>
+      </c>
+      <c r="L18" t="s" s="2">
+        <v>134</v>
+      </c>
       <c r="M18" t="s" s="2">
-        <v>138</v>
+        <v>118</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2742,7 +2788,7 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>139</v>
+        <v>119</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>80</v>
@@ -2762,23 +2808,21 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E19" t="s" s="2">
-        <v>141</v>
-      </c>
+      <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -2790,12 +2834,10 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>101</v>
+        <v>136</v>
       </c>
       <c r="L19" s="2"/>
-      <c r="M19" t="s" s="2">
-        <v>142</v>
-      </c>
+      <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -2845,13 +2887,13 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>143</v>
+        <v>135</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>74</v>
@@ -2865,23 +2907,21 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E20" t="s" s="2">
-        <v>145</v>
-      </c>
+      <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>74</v>
@@ -2893,12 +2933,10 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>101</v>
+        <v>138</v>
       </c>
       <c r="L20" s="2"/>
-      <c r="M20" t="s" s="2">
-        <v>146</v>
-      </c>
+      <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -2924,13 +2962,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y20" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>139</v>
+      </c>
+      <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>74</v>
+        <v>140</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2948,7 +2984,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -2968,23 +3004,23 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>148</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E21" t="s" s="2">
-        <v>149</v>
+        <v>84</v>
       </c>
       <c r="F21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -2996,11 +3032,11 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="L21" s="2"/>
       <c r="M21" t="s" s="2">
-        <v>150</v>
+        <v>86</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3027,13 +3063,11 @@
         <v>74</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y21" t="s" s="2">
-        <v>74</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="Y21" s="2"/>
       <c r="Z21" t="s" s="2">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>74</v>
@@ -3051,7 +3085,7 @@
         <v>74</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>151</v>
+        <v>89</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>80</v>
@@ -3071,21 +3105,23 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>142</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" t="s" s="2">
+        <v>62</v>
+      </c>
       <c r="F22" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>74</v>
@@ -3097,11 +3133,11 @@
         <v>74</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>153</v>
+        <v>85</v>
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3152,7 +3188,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3172,21 +3208,23 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E23" s="2"/>
+      <c r="E23" t="s" s="2">
+        <v>146</v>
+      </c>
       <c r="F23" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="H23" t="s" s="2">
         <v>74</v>
@@ -3198,11 +3236,11 @@
         <v>74</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3253,7 +3291,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3273,17 +3311,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>80</v>
@@ -3301,11 +3339,11 @@
         <v>74</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>161</v>
+        <v>102</v>
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3356,7 +3394,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3376,17 +3414,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3404,11 +3442,11 @@
         <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3459,13 +3497,13 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>74</v>
@@ -3479,23 +3517,23 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3507,11 +3545,11 @@
         <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>171</v>
+        <v>102</v>
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3562,13 +3600,13 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>74</v>
@@ -3582,10 +3620,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3596,7 +3634,7 @@
         <v>80</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H27" t="s" s="2">
         <v>74</v>
@@ -3608,10 +3646,12 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>175</v>
+        <v>162</v>
       </c>
       <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
+      <c r="M27" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3661,13 +3701,13 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>74</v>
@@ -3681,10 +3721,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3695,7 +3735,7 @@
         <v>80</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>74</v>
@@ -3707,10 +3747,12 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>177</v>
+        <v>102</v>
       </c>
       <c r="L28" s="2"/>
-      <c r="M28" s="2"/>
+      <c r="M28" t="s" s="2">
+        <v>166</v>
+      </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -3760,13 +3802,13 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>176</v>
+        <v>167</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>74</v>
@@ -3780,16 +3822,18 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E29" s="2"/>
+      <c r="E29" t="s" s="2">
+        <v>169</v>
+      </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
       </c>
@@ -3806,10 +3850,12 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="L29" s="2"/>
-      <c r="M29" s="2"/>
+      <c r="M29" t="s" s="2">
+        <v>171</v>
+      </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3859,7 +3905,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>178</v>
+        <v>172</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3879,21 +3925,23 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" t="s" s="2">
+        <v>174</v>
+      </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G30" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="H30" t="s" s="2">
         <v>74</v>
@@ -3905,10 +3953,12 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="L30" s="2"/>
-      <c r="M30" s="2"/>
+      <c r="M30" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -3958,13 +4008,13 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AH30" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI30" t="s" s="2">
         <v>74</v>
@@ -3978,21 +4028,23 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>74</v>
@@ -4004,10 +4056,12 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="L31" s="2"/>
-      <c r="M31" s="2"/>
+      <c r="M31" t="s" s="2">
+        <v>181</v>
+      </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4063,7 +4117,7 @@
         <v>80</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>74</v>
@@ -4077,10 +4131,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4088,10 +4142,10 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>74</v>
@@ -4103,7 +4157,7 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>95</v>
+        <v>184</v>
       </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -4156,13 +4210,13 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>74</v>
@@ -4171,6 +4225,501 @@
         <v>74</v>
       </c>
       <c r="AK32" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>186</v>
+      </c>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>185</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK33" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK34" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK35" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK36" t="s" s="2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>193</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AK37" t="s" s="2">
         <v>74</v>
       </c>
     </row>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-17T15:05:21+00:00</t>
+    <t>2025-02-03T10:34:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1197" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1203" uniqueCount="200">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-03T10:34:19+00:00</t>
+    <t>2025-02-05T14:18:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -402,6 +402,9 @@
   </si>
   <si>
     <t>AssignedEntity.id</t>
+  </si>
+  <si>
+    <t>Identifiant du responsable</t>
   </si>
   <si>
     <t>AssignedEntity.id.nullFlavor</t>
@@ -429,7 +432,9 @@
     <t>AssignedEntity.id.extension</t>
   </si>
   <si>
-    <t>Valeur de l’identifiant</t>
+    <t>Valeur de l’identifiant.
+- Pour le PS, valeur de PS_IdNat (voir CI-SIS_ANX_SOURCES-DONNEES-PERSONNES-STRUCTURES).
+- Pour le patient/usager, valeur de l'INS du patient/usager.</t>
   </si>
   <si>
     <t>AssignedEntity.sdtcIdentifiedBy</t>
@@ -446,6 +451,9 @@
 </t>
   </si>
   <si>
+    <t>Profession ou rôle du responsable</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -589,6 +597,9 @@
 </t>
   </si>
   <si>
+    <t>Adresse géopostale</t>
+  </si>
+  <si>
     <t>AssignedEntity.telecom</t>
   </si>
   <si>
@@ -596,6 +607,9 @@
 </t>
   </si>
   <si>
+    <t>Coordonnées télécom</t>
+  </si>
+  <si>
     <t>AssignedEntity.assignedPerson</t>
   </si>
   <si>
@@ -603,11 +617,23 @@
 </t>
   </si>
   <si>
+    <t>Personne physique : 
+- Obligatoire pour un professionnel 
+- Obligatoire pour un patient/usager 
+- Non utilisé pour un SNR 
+- Non utilisé pour le DP</t>
+  </si>
+  <si>
     <t>AssignedEntity.representedOrganization</t>
   </si>
   <si>
     <t xml:space="preserve">http://hl7.org/cda/stds/core/StructureDefinition/Organization {https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-core-represented-organization}
 </t>
+  </si>
+  <si>
+    <t>Structure de rattachement :
+- Pour un PS : Organisation pour le compte de laquelle intervient le PS.
+- Pour un patient : seul l'élément standardIndustryClassCode est renseigné (cas particulier des documents d'expression personnelle du patient).</t>
   </si>
   <si>
     <t>AssignedEntity.sdtcPatient</t>
@@ -2220,7 +2246,9 @@
       <c r="K13" t="s" s="2">
         <v>95</v>
       </c>
-      <c r="L13" s="2"/>
+      <c r="L13" t="s" s="2">
+        <v>127</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2291,10 +2319,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2392,10 +2420,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2495,10 +2523,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2598,10 +2626,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2629,10 +2657,10 @@
         <v>112</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2703,10 +2731,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2734,7 +2762,7 @@
         <v>102</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
         <v>118</v>
@@ -2808,10 +2836,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2834,7 +2862,7 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -2887,7 +2915,7 @@
         <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -2907,10 +2935,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2933,9 +2961,11 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="L20" s="2"/>
+        <v>139</v>
+      </c>
+      <c r="L20" t="s" s="2">
+        <v>140</v>
+      </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2962,11 +2992,11 @@
         <v>74</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="Y20" s="2"/>
       <c r="Z20" t="s" s="2">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>74</v>
@@ -2984,7 +3014,7 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>80</v>
@@ -3004,10 +3034,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3105,10 +3135,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3137,7 +3167,7 @@
       </c>
       <c r="L22" s="2"/>
       <c r="M22" t="s" s="2">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3188,7 +3218,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>80</v>
@@ -3208,17 +3238,17 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E23" t="s" s="2">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="F23" t="s" s="2">
         <v>80</v>
@@ -3240,7 +3270,7 @@
       </c>
       <c r="L23" s="2"/>
       <c r="M23" t="s" s="2">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3291,7 +3321,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>80</v>
@@ -3311,17 +3341,17 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E24" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F24" t="s" s="2">
         <v>80</v>
@@ -3343,7 +3373,7 @@
       </c>
       <c r="L24" s="2"/>
       <c r="M24" t="s" s="2">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3394,7 +3424,7 @@
         <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>80</v>
@@ -3414,17 +3444,17 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E25" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="F25" t="s" s="2">
         <v>80</v>
@@ -3446,7 +3476,7 @@
       </c>
       <c r="L25" s="2"/>
       <c r="M25" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3497,7 +3527,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -3517,17 +3547,17 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E26" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F26" t="s" s="2">
         <v>80</v>
@@ -3549,7 +3579,7 @@
       </c>
       <c r="L26" s="2"/>
       <c r="M26" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3600,7 +3630,7 @@
         <v>74</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -3620,10 +3650,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3646,11 +3676,11 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="L27" s="2"/>
       <c r="M27" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3701,7 +3731,7 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -3721,10 +3751,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3751,7 +3781,7 @@
       </c>
       <c r="L28" s="2"/>
       <c r="M28" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3802,7 +3832,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -3822,17 +3852,17 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E29" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F29" t="s" s="2">
         <v>80</v>
@@ -3850,11 +3880,11 @@
         <v>74</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="L29" s="2"/>
       <c r="M29" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3905,7 +3935,7 @@
         <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -3925,17 +3955,17 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E30" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F30" t="s" s="2">
         <v>80</v>
@@ -3953,11 +3983,11 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="L30" s="2"/>
       <c r="M30" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4008,7 +4038,7 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -4028,17 +4058,17 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E31" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F31" t="s" s="2">
         <v>80</v>
@@ -4056,11 +4086,11 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="L31" s="2"/>
       <c r="M31" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4111,7 +4141,7 @@
         <v>74</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -4131,10 +4161,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4157,9 +4187,11 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>184</v>
-      </c>
-      <c r="L32" s="2"/>
+        <v>186</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="M32" s="2"/>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4210,7 +4242,7 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -4230,10 +4262,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4256,9 +4288,11 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="L33" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>190</v>
+      </c>
       <c r="M33" s="2"/>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4309,7 +4343,7 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -4329,10 +4363,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4355,9 +4389,11 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L34" s="2"/>
+        <v>192</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>193</v>
+      </c>
       <c r="M34" s="2"/>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4408,7 +4444,7 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -4428,10 +4464,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4454,9 +4490,11 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>190</v>
-      </c>
-      <c r="L35" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>196</v>
+      </c>
       <c r="M35" s="2"/>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4507,7 +4545,7 @@
         <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -4527,10 +4565,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4553,7 +4591,7 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
@@ -4606,7 +4644,7 @@
         <v>74</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -4626,10 +4664,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4705,7 +4743,7 @@
         <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>75</v>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T14:18:33+00:00</t>
+    <t>2025-02-05T15:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:17:43+00:00</t>
+    <t>2025-02-05T15:35:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-05T15:35:39+00:00</t>
+    <t>2025-02-06T13:21:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>AssignedEntity est utilisé dans les éléments suivants : dataEnterer, informant, legalAuthenticator, authenticator, performer, responsibleParty et encounterParticipant.</t>
+    <t>L'élément de l'en-tête du CDA assignedEntity est utilisé dans les éléments suivants : dataEnterer, informant, legalAuthenticator, authenticator, performer, responsibleParty et encounterParticipant.</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
+++ b/SBM-initDocIG/ig/StructureDefinition-fr-core-assigned-entity.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-06T13:21:10+00:00</t>
+    <t>2025-02-06T13:38:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
